--- a/Inputs_Projets_NF26_AI07/Hopital Mapping VF2026.xlsx
+++ b/Inputs_Projets_NF26_AI07/Hopital Mapping VF2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mchebou/Documents/09.UTC/NF26/Présentations/2026/Data_Hospital/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\etien\OneDrive\Bureau\Cours\Y4\P26\NF26\Projets\projet_smartTeem\NF26_Smart_Teem\Inputs_Projets_NF26_AI07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403708FC-AE4F-B742-A213-C889DDA954C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E2F08F-D599-4544-9D0B-793EB66F39AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{783B3F39-6BFD-C940-8606-2E6B97310E4C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" activeTab="1" xr2:uid="{783B3F39-6BFD-C940-8606-2E6B97310E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Staging" sheetId="1" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -986,7 +975,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1543,22 +1532,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769CA4DD-88B4-584F-8493-2F25A9DD02C6}">
   <dimension ref="A1:J69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="29.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="1"/>
-    <col min="6" max="6" width="25.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
-    <col min="10" max="10" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="1"/>
+    <col min="5" max="5" width="10.81640625" style="1"/>
+    <col min="6" max="6" width="25.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="1"/>
+    <col min="10" max="10" width="48.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="20" t="s">
         <v>137</v>
       </c>
@@ -1574,7 +1563,7 @@
       <c r="I1" s="22"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>134</v>
       </c>
@@ -1606,7 +1595,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1638,7 +1627,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1670,7 +1659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1702,7 +1691,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1734,7 +1723,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1751,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1794,7 +1783,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1826,7 +1815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -1858,7 +1847,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1890,7 +1879,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -1922,7 +1911,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -1954,7 +1943,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
@@ -1982,7 +1971,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2014,7 +2003,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
@@ -2046,7 +2035,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -2078,7 +2067,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -2110,7 +2099,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
@@ -2142,7 +2131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
@@ -2174,7 +2163,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
@@ -2206,7 +2195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
@@ -2238,7 +2227,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
@@ -2266,7 +2255,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
         <v>13</v>
       </c>
@@ -2294,7 +2283,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
@@ -2326,7 +2315,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
         <v>13</v>
       </c>
@@ -2358,7 +2347,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
         <v>13</v>
       </c>
@@ -2390,7 +2379,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="5" t="s">
         <v>23</v>
       </c>
@@ -2422,7 +2411,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="5" t="s">
         <v>23</v>
       </c>
@@ -2454,7 +2443,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="5" t="s">
         <v>23</v>
       </c>
@@ -2486,7 +2475,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="5" t="s">
         <v>23</v>
       </c>
@@ -2514,7 +2503,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="5" t="s">
         <v>23</v>
       </c>
@@ -2542,7 +2531,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="5" t="s">
         <v>23</v>
       </c>
@@ -2570,7 +2559,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="5" t="s">
         <v>23</v>
       </c>
@@ -2598,7 +2587,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="5" t="s">
         <v>23</v>
       </c>
@@ -2626,7 +2615,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="5" t="s">
         <v>23</v>
       </c>
@@ -2654,7 +2643,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="5" t="s">
         <v>23</v>
       </c>
@@ -2682,7 +2671,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="5" t="s">
         <v>23</v>
       </c>
@@ -2710,7 +2699,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" s="5" t="s">
         <v>23</v>
       </c>
@@ -2738,7 +2727,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" s="5" t="s">
         <v>23</v>
       </c>
@@ -2766,7 +2755,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" s="5" t="s">
         <v>23</v>
       </c>
@@ -2794,7 +2783,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="A42" s="5" t="s">
         <v>23</v>
       </c>
@@ -2822,7 +2811,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43" s="5" t="s">
         <v>23</v>
       </c>
@@ -2854,7 +2843,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44" s="5" t="s">
         <v>23</v>
       </c>
@@ -2886,7 +2875,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
         <v>40</v>
       </c>
@@ -2918,7 +2907,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
         <v>40</v>
       </c>
@@ -2950,7 +2939,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
         <v>40</v>
       </c>
@@ -2982,7 +2971,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
         <v>40</v>
       </c>
@@ -3014,7 +3003,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
         <v>40</v>
       </c>
@@ -3046,7 +3035,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
         <v>40</v>
       </c>
@@ -3078,7 +3067,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
         <v>40</v>
       </c>
@@ -3106,7 +3095,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
         <v>40</v>
       </c>
@@ -3134,7 +3123,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
         <v>40</v>
       </c>
@@ -3162,7 +3151,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
         <v>40</v>
       </c>
@@ -3190,7 +3179,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
         <v>40</v>
       </c>
@@ -3218,7 +3207,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
         <v>40</v>
       </c>
@@ -3246,7 +3235,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
         <v>40</v>
       </c>
@@ -3274,7 +3263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -3306,7 +3295,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59" s="5" t="s">
         <v>58</v>
       </c>
@@ -3338,7 +3327,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10">
       <c r="A60" s="5" t="s">
         <v>58</v>
       </c>
@@ -3370,7 +3359,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10">
       <c r="A61" s="5" t="s">
         <v>58</v>
       </c>
@@ -3402,7 +3391,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10">
       <c r="A62" s="5" t="s">
         <v>58</v>
       </c>
@@ -3434,7 +3423,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10">
       <c r="A63" s="5" t="s">
         <v>58</v>
       </c>
@@ -3466,7 +3455,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10">
       <c r="A64" s="5" t="s">
         <v>58</v>
       </c>
@@ -3498,7 +3487,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
         <v>57</v>
       </c>
@@ -3530,7 +3519,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
         <v>57</v>
       </c>
@@ -3562,7 +3551,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
         <v>57</v>
       </c>
@@ -3594,7 +3583,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
         <v>57</v>
       </c>
@@ -3626,7 +3615,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
         <v>57</v>
       </c>
@@ -3665,6 +3654,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF Confidentialité: Restreint</oddFooter>
   </headerFooter>
@@ -3674,22 +3664,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CAFCA74-9FC5-C241-99E0-C2C69841C5BE}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="49.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" s="20" t="s">
         <v>137</v>
       </c>
@@ -3710,7 +3700,7 @@
       <c r="N1" s="25"/>
       <c r="O1" s="26"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="6" t="s">
         <v>140</v>
       </c>
@@ -3757,7 +3747,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15.6">
       <c r="A3" s="4" t="s">
         <v>144</v>
       </c>
@@ -3804,7 +3794,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="15.6">
       <c r="A4" s="4" t="s">
         <v>144</v>
       </c>
@@ -3847,7 +3837,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="15.6">
       <c r="A5" s="4" t="s">
         <v>144</v>
       </c>
@@ -3890,7 +3880,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="15.6">
       <c r="A6" s="4" t="s">
         <v>144</v>
       </c>
@@ -3933,7 +3923,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="15.6">
       <c r="A7" s="4" t="s">
         <v>144</v>
       </c>
@@ -3972,7 +3962,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="15.6">
       <c r="A8" s="4" t="s">
         <v>144</v>
       </c>
@@ -4015,7 +4005,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="15.6">
       <c r="A9" s="4" t="s">
         <v>144</v>
       </c>
@@ -4058,7 +4048,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="15.6">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4091,7 +4081,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="15.6">
       <c r="A11" s="5" t="s">
         <v>144</v>
       </c>
@@ -4138,7 +4128,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="85" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="78">
       <c r="A12" s="5" t="s">
         <v>144</v>
       </c>
@@ -4177,7 +4167,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="15.6">
       <c r="A13" s="5" t="s">
         <v>144</v>
       </c>
@@ -4216,7 +4206,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="15.6">
       <c r="A14" s="5" t="s">
         <v>144</v>
       </c>
@@ -4259,7 +4249,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="15.6">
       <c r="A15" s="5" t="s">
         <v>144</v>
       </c>
@@ -4302,7 +4292,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="15.6">
       <c r="A16" s="5" t="s">
         <v>144</v>
       </c>
@@ -4345,7 +4335,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="15.6">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -4378,7 +4368,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="46.8">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4415,7 +4405,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="15.6">
       <c r="A19" s="4" t="s">
         <v>144</v>
       </c>
@@ -4458,7 +4448,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="15.6">
       <c r="A20" s="4" t="s">
         <v>144</v>
       </c>
@@ -4501,7 +4491,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="46.8">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -4536,7 +4526,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="15.6">
       <c r="A22" s="5" t="s">
         <v>144</v>
       </c>
@@ -4579,7 +4569,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="15.6">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -4612,7 +4602,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="62.4">
       <c r="A24" s="4" t="s">
         <v>144</v>
       </c>
@@ -4657,7 +4647,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="15.6">
       <c r="A25" s="4" t="s">
         <v>144</v>
       </c>
@@ -4700,7 +4690,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="15.6">
       <c r="A26" s="4" t="s">
         <v>144</v>
       </c>
@@ -4743,7 +4733,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="15.6">
       <c r="A27" s="4" t="s">
         <v>144</v>
       </c>
@@ -4786,7 +4776,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="15.6">
       <c r="A28" s="4" t="s">
         <v>144</v>
       </c>
@@ -4829,7 +4819,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="15.6">
       <c r="A29" s="4" t="s">
         <v>144</v>
       </c>
@@ -4872,7 +4862,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="15.6">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -4905,7 +4895,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="62.4">
       <c r="A31" s="5" t="s">
         <v>144</v>
       </c>
@@ -4950,7 +4940,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="15.6">
       <c r="A32" s="5" t="s">
         <v>144</v>
       </c>
@@ -4993,7 +4983,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="15.6">
       <c r="A33" s="5" t="s">
         <v>144</v>
       </c>
@@ -5032,7 +5022,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="15.6">
       <c r="A34" s="5" t="s">
         <v>144</v>
       </c>
@@ -5071,7 +5061,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="15.6">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -5104,7 +5094,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="62.4">
       <c r="A36" s="4" t="s">
         <v>144</v>
       </c>
@@ -5151,7 +5141,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="15.6">
       <c r="A37" s="4" t="s">
         <v>144</v>
       </c>
@@ -5194,7 +5184,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="15.6">
       <c r="A38" s="4" t="s">
         <v>144</v>
       </c>
@@ -5237,7 +5227,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="15.6">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -5270,7 +5260,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="15.6">
       <c r="A40" s="4" t="s">
         <v>144</v>
       </c>
@@ -5313,7 +5303,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="15.6">
       <c r="A41" s="4" t="s">
         <v>144</v>
       </c>
@@ -5356,7 +5346,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="15.6">
       <c r="A42" s="4" t="s">
         <v>144</v>
       </c>
@@ -5395,7 +5385,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="15.6">
       <c r="A43" s="4" t="s">
         <v>144</v>
       </c>
@@ -5434,7 +5424,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="15.6">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -5473,7 +5463,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="15.6">
       <c r="A45" s="4" t="s">
         <v>144</v>
       </c>
@@ -5512,7 +5502,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="15.6">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -5545,7 +5535,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="62.4">
       <c r="A47" s="5" t="s">
         <v>144</v>
       </c>
@@ -5592,7 +5582,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="15.6">
       <c r="A48" s="5" t="s">
         <v>144</v>
       </c>
@@ -5631,7 +5621,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="15.6">
       <c r="A49" s="5" t="s">
         <v>144</v>
       </c>
@@ -5672,7 +5662,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="15.6">
       <c r="A50" s="5" t="s">
         <v>144</v>
       </c>
@@ -5717,7 +5707,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="15.6">
       <c r="A51" s="5" t="s">
         <v>144</v>
       </c>
@@ -5760,7 +5750,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" ht="15.6">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -5793,7 +5783,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="62.4">
       <c r="A53" s="4" t="s">
         <v>144</v>
       </c>
@@ -5840,7 +5830,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="15.6">
       <c r="A54" s="4" t="s">
         <v>144</v>
       </c>
@@ -5881,7 +5871,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="15.6">
       <c r="A55" s="4" t="s">
         <v>144</v>
       </c>
@@ -5922,7 +5912,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="15.6">
       <c r="A56" s="4" t="s">
         <v>144</v>
       </c>
@@ -5961,7 +5951,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" ht="15.6">
       <c r="A57" s="4" t="s">
         <v>144</v>
       </c>
@@ -6002,7 +5992,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="15.6">
       <c r="A58" s="4" t="s">
         <v>144</v>
       </c>
@@ -6041,7 +6031,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="15.6">
       <c r="A59" s="4" t="s">
         <v>144</v>
       </c>
@@ -6080,7 +6070,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="15.6">
       <c r="A60" s="4" t="s">
         <v>144</v>
       </c>
@@ -6125,7 +6115,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="15.6">
       <c r="A61" s="4" t="s">
         <v>144</v>
       </c>
@@ -6168,7 +6158,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="15.6">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -6201,7 +6191,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="15.6">
       <c r="A63" s="5" t="s">
         <v>144</v>
       </c>
@@ -6246,7 +6236,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="62.4">
       <c r="A64" s="5" t="s">
         <v>144</v>
       </c>
@@ -6289,7 +6279,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" ht="62.4">
       <c r="A65" s="5" t="s">
         <v>144</v>
       </c>
@@ -6334,7 +6324,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" ht="15.6">
       <c r="A66" s="5" t="s">
         <v>144</v>
       </c>
@@ -6377,7 +6367,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" ht="15.6">
       <c r="A67" s="5" t="s">
         <v>144</v>
       </c>
@@ -6420,7 +6410,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" ht="15.6">
       <c r="A68" s="5" t="s">
         <v>144</v>
       </c>
@@ -6463,7 +6453,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" ht="15.6">
       <c r="A69" s="5" t="s">
         <v>144</v>
       </c>
@@ -6502,7 +6492,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" ht="15.6">
       <c r="A70" s="5" t="s">
         <v>144</v>
       </c>
@@ -6541,7 +6531,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" ht="15.6">
       <c r="A71" s="5" t="s">
         <v>144</v>
       </c>
@@ -6580,7 +6570,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" ht="15.6">
       <c r="A72" s="5" t="s">
         <v>144</v>
       </c>
@@ -6619,7 +6609,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" ht="15.6">
       <c r="A73" s="5" t="s">
         <v>144</v>
       </c>
@@ -6658,7 +6648,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" ht="15.6">
       <c r="A74" s="5" t="s">
         <v>144</v>
       </c>
@@ -6697,7 +6687,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" ht="15.6">
       <c r="A75" s="5" t="s">
         <v>144</v>
       </c>
@@ -6736,7 +6726,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" ht="15.6">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -6769,7 +6759,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" ht="15.6">
       <c r="A77" s="4" t="s">
         <v>144</v>
       </c>
@@ -6814,7 +6804,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" ht="15.6">
       <c r="A78" s="4" t="s">
         <v>144</v>
       </c>
@@ -6859,7 +6849,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" ht="15.6">
       <c r="A79" s="4" t="s">
         <v>144</v>
       </c>
@@ -6902,7 +6892,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" ht="15.6">
       <c r="A80" s="4" t="s">
         <v>144</v>
       </c>
@@ -6945,7 +6935,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" ht="15.6">
       <c r="A81" s="4" t="s">
         <v>144</v>
       </c>
@@ -6988,7 +6978,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" ht="15.6">
       <c r="A82" s="4" t="s">
         <v>144</v>
       </c>
@@ -7031,7 +7021,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" ht="62.4">
       <c r="A83" s="4" t="s">
         <v>144</v>
       </c>
@@ -7074,7 +7064,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" ht="15.6">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -7107,7 +7097,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" ht="62.4">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -7144,7 +7134,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" ht="15.6">
       <c r="A86" s="5" t="s">
         <v>144</v>
       </c>
@@ -7187,7 +7177,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" ht="15.6">
       <c r="A87" s="5" t="s">
         <v>144</v>
       </c>
@@ -7230,7 +7220,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" ht="15.6">
       <c r="A88" s="5" t="s">
         <v>144</v>
       </c>
@@ -7273,7 +7263,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" ht="15.6">
       <c r="A89" s="5" t="s">
         <v>144</v>
       </c>
@@ -7316,7 +7306,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" ht="15.6">
       <c r="A90" s="5" t="s">
         <v>144</v>
       </c>
@@ -7359,7 +7349,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" ht="15.6">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -7392,7 +7382,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" ht="15.6">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -7427,7 +7417,7 @@
       </c>
       <c r="O92" s="13"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" ht="15.6">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -7460,7 +7450,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" ht="15.6">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -7491,7 +7481,7 @@
       </c>
       <c r="O94" s="13"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" ht="15.6">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -7520,7 +7510,7 @@
       </c>
       <c r="O95" s="13"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" ht="15.6">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -7553,7 +7543,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" ht="15.6">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -7588,7 +7578,7 @@
       </c>
       <c r="O97" s="14"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" ht="15.6">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -7619,7 +7609,7 @@
       </c>
       <c r="O98" s="14"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" ht="15.6">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -7648,7 +7638,7 @@
       </c>
       <c r="O99" s="14"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" ht="15.6">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -7687,6 +7677,7 @@
     <mergeCell ref="F1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF Confidentialité: Restreint</oddFooter>
   </headerFooter>
